--- a/artfynd/A 14858-2022 artfynd.xlsx
+++ b/artfynd/A 14858-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14858-2022 artfynd.xlsx
+++ b/artfynd/A 14858-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>81780617</v>
       </c>
       <c r="B2" t="n">
-        <v>89803</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553700.8380875541</v>
+        <v>553701</v>
       </c>
       <c r="R2" t="n">
-        <v>6304530.26278223</v>
+        <v>6304530</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,6 +793,241 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>102764564</v>
+      </c>
+      <c r="B3" t="n">
+        <v>42292</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100564</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rosenryggat ordensfly</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Catocala pacta</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Smedjeviks NR Nybro, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>553615</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6304488</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl-Erik Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl-Erik Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102764666</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smedjeviks NR Nybro, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>553615</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6304488</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl-Erik Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl-Erik Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14858-2022 artfynd.xlsx
+++ b/artfynd/A 14858-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81780617</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102764564</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,8 +1043,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102764666</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>